--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/INDIANA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/INDIANA_2014.xlsx
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C264">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C274">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C685">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C778">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C779">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C811">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1172">
@@ -24540,7 +24540,7 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1344">
